--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484204_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484204_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7204</v>
+        <v>4.9444</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7694</v>
+        <v>4.8299</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0489</v>
+        <v>0.1145</v>
       </c>
       <c r="G2" t="n">
         <v>2.6864</v>
@@ -610,13 +610,13 @@
         <v>1.5627</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0907</v>
+        <v>-0.8667</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4153</v>
+        <v>-0.3548</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6754</v>
+        <v>-0.5119</v>
       </c>
       <c r="V2" t="n">
         <v>3.7107</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.982</v>
+        <v>3.4491</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9259</v>
+        <v>3.4203</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0561</v>
+        <v>0.0288</v>
       </c>
       <c r="G3" t="n">
         <v>-0.6211</v>
@@ -688,13 +688,13 @@
         <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7165</v>
+        <v>0.1837</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4404</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2761</v>
+        <v>0.2489</v>
       </c>
       <c r="V3" t="n">
         <v>2.7145</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.666</v>
+        <v>1.7718</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4242</v>
+        <v>1.9386</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2418</v>
+        <v>-0.1667</v>
       </c>
       <c r="G4" t="n">
         <v>3.4528</v>
@@ -766,13 +766,13 @@
         <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6355</v>
+        <v>-0.2587</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4404</v>
+        <v>-0.0453</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1951</v>
+        <v>-0.2134</v>
       </c>
       <c r="V4" t="n">
         <v>-0.0549</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4888</v>
+        <v>1.0493</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8177</v>
+        <v>1.5144</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3289</v>
+        <v>-0.4651</v>
       </c>
       <c r="G5" t="n">
         <v>0.8448</v>
@@ -844,13 +844,13 @@
         <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2807</v>
+        <v>-0.7202</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1899</v>
+        <v>-0.1134</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4706</v>
+        <v>-0.6068</v>
       </c>
       <c r="V5" t="n">
         <v>1.7061</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.58</v>
+        <v>0.8566</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2231</v>
+        <v>1.4452</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6431</v>
+        <v>-0.5886</v>
       </c>
       <c r="G6" t="n">
         <v>0.7528</v>
@@ -922,13 +922,13 @@
         <v>1.5627</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5635</v>
+        <v>-0.2869</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3548</v>
+        <v>-0.1326</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2087</v>
+        <v>-0.1542</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3506</v>
+        <v>0.7356</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7858000000000001</v>
+        <v>1.0892</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4352</v>
+        <v>-0.3535</v>
       </c>
       <c r="G7" t="n">
         <v>0.2226</v>
@@ -1000,13 +1000,13 @@
         <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9222</v>
+        <v>-0.5372</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6052</v>
+        <v>-0.3019</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.317</v>
+        <v>-0.2353</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1219</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0106</v>
+        <v>0.1105</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4942</v>
+        <v>-1.3731</v>
       </c>
       <c r="F8" t="n">
         <v>1.4836</v>
@@ -1078,10 +1078,10 @@
         <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4374</v>
+        <v>0.5585</v>
       </c>
       <c r="T8" t="n">
-        <v>0.311</v>
+        <v>0.432</v>
       </c>
       <c r="U8" t="n">
         <v>0.1265</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4725</v>
+        <v>-1.2781</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9607</v>
+        <v>-0.6574</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5118</v>
+        <v>-0.6207</v>
       </c>
       <c r="G9" t="n">
         <v>0.5724</v>
@@ -1156,13 +1156,13 @@
         <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7743</v>
+        <v>-0.5799</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6657</v>
+        <v>-0.3624</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1085</v>
+        <v>-0.2175</v>
       </c>
       <c r="V9" t="n">
         <v>0.4875</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5054</v>
+        <v>-2.9862</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3926</v>
+        <v>-1.7931</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1127</v>
+        <v>-1.1931</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8397</v>
+        <v>-1.953</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.1622</v>
+        <v>-1.6963</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3225</v>
+        <v>-0.2566</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8318</v>
+        <v>0.3742</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5705</v>
+        <v>-0.449</v>
       </c>
       <c r="L10" t="n">
-        <v>2.4023</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.6714</v>
+        <v>-2.3271</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5917</v>
+        <v>-1.2474</v>
       </c>
       <c r="O10" t="n">
         <v>-1.0797</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3674</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9301</v>
+        <v>-2.1488</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1764</v>
+        <v>-0.13</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2943</v>
+        <v>-0.0185</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8822</v>
+        <v>-0.1116</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1219</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9512</v>
+        <v>-3.1997</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6219</v>
+        <v>-1.3321</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3293</v>
+        <v>-1.8676</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.953</v>
+        <v>-0.8397</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6963</v>
+        <v>-2.1622</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2566</v>
+        <v>1.3225</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3742</v>
+        <v>1.8318</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.449</v>
+        <v>-0.5705</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8231000000000001</v>
+        <v>2.4023</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.3271</v>
+        <v>-2.6714</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2474</v>
+        <v>-1.5917</v>
       </c>
       <c r="O11" t="n">
         <v>-1.0797</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7814</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1488</v>
+        <v>-2.9301</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.095</v>
+        <v>-0.8708</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.2337</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2477</v>
+        <v>-0.6371</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1219</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.848100000000001</v>
+        <v>5.453299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>8.476700000000001</v>
+        <v>9.081899999999997</v>
       </c>
       <c r="F12" t="n">
         <v>-3.6284</v>
@@ -1366,7 +1366,7 @@
         <v>20.8015</v>
       </c>
       <c r="K12" t="n">
-        <v>9.330900000000002</v>
+        <v>9.3309</v>
       </c>
       <c r="L12" t="n">
         <v>11.4707</v>
@@ -1375,7 +1375,7 @@
         <v>-15.1546</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.078900000000001</v>
+        <v>-9.078899999999999</v>
       </c>
       <c r="O12" t="n">
         <v>-6.075799999999999</v>
@@ -1390,10 +1390,10 @@
         <v>13.674</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.1134</v>
+        <v>-3.5082</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.8009</v>
+        <v>-1.1958</v>
       </c>
       <c r="U12" t="n">
         <v>-2.3124</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.1295</v>
+        <v>4.6702</v>
       </c>
       <c r="E13" t="n">
-        <v>5.8345</v>
+        <v>6.239</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.705</v>
+        <v>-1.5688</v>
       </c>
       <c r="G13" t="n">
         <v>4.3507</v>
@@ -1468,13 +1468,13 @@
         <v>1.9534</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3466</v>
+        <v>0.194</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2943</v>
+        <v>0.1102</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0524</v>
+        <v>0.0838</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8279</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7193</v>
+        <v>1.2992</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1479</v>
+        <v>0.9456</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5715</v>
+        <v>0.3536</v>
       </c>
       <c r="G14" t="n">
         <v>1.0564</v>
@@ -1546,13 +1546,13 @@
         <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>0.581</v>
+        <v>0.1609</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1294</v>
+        <v>-0.0728</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4516</v>
+        <v>0.2337</v>
       </c>
       <c r="V14" t="n">
         <v>0.2772</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>F. VIEJO ANDREU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8144</v>
+        <v>0.479</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9259</v>
+        <v>2.3</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1116</v>
+        <v>-1.821</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2105</v>
+        <v>-0.9133</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3512</v>
+        <v>-1.0619</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.5618</v>
+        <v>0.1486</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1767</v>
+        <v>2.8226</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5239</v>
+        <v>0.2456</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.3472</v>
+        <v>2.577</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.3872</v>
+        <v>-3.7358</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1727</v>
+        <v>-1.3075</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2146</v>
+        <v>-2.4283</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0482</v>
+        <v>0.8062</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4254</v>
+        <v>0.4541</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6228</v>
+        <v>0.3521</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1588</v>
+        <v>0.024</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0009</v>
+        <v>0.102</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1597</v>
+        <v>-0.078</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2133</v>
@@ -1702,13 +1702,13 @@
         <v>0.1953</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1409</v>
+        <v>0.0419</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0605</v>
+        <v>0.0406</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0803</v>
+        <v>0.0014</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3525</v>
+        <v>-0.0569</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0677</v>
+        <v>1.2181</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4202</v>
+        <v>-1.275</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0758</v>
+        <v>-0.2105</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0373</v>
+        <v>2.3512</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0385</v>
+        <v>-2.5618</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0827</v>
+        <v>2.1767</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7163</v>
+        <v>3.5239</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-1.3472</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1585</v>
+        <v>-2.3872</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7536</v>
+        <v>-1.1727</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4049</v>
+        <v>-1.2146</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7699</v>
+        <v>1.177</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9851</v>
+        <v>0.7176</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2152</v>
+        <v>0.4593</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2186</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. VIEJO ANDREU</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3844</v>
+        <v>-0.6776</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4911</v>
+        <v>1.19</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8755</v>
+        <v>-1.8676</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9133</v>
+        <v>-1.0983</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0619</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1486</v>
+        <v>-0.5928</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8226</v>
+        <v>2.0377</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2456</v>
+        <v>1.4159</v>
       </c>
       <c r="L18" t="n">
-        <v>2.577</v>
+        <v>0.6218</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.7358</v>
+        <v>-3.136</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3075</v>
+        <v>-1.9215</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.4283</v>
+        <v>-1.2146</v>
       </c>
       <c r="P18" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>2.3441</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0572</v>
+        <v>0.604</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3548</v>
+        <v>0.461</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2976</v>
+        <v>0.143</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.5507</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8254</v>
+        <v>-0.7048</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9877</v>
+        <v>-0.696</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8131</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0983</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5054999999999999</v>
+        <v>1.2653</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5928</v>
+        <v>-0.3243</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0377</v>
+        <v>1.7003</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4159</v>
+        <v>1.6193</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6218</v>
+        <v>0.0809</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.136</v>
+        <v>-0.7593</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9215</v>
+        <v>-0.354</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2146</v>
+        <v>-0.4052</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3441</v>
+        <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4562</v>
+        <v>-0.3453</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2588</v>
+        <v>-0.4429</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1974</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5507</v>
+        <v>-1.4959</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>M. FENÉS HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1365</v>
+        <v>-0.7764</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1005</v>
+        <v>0.5622</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0361</v>
+        <v>-1.3385</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9409999999999999</v>
+        <v>-1.0758</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2653</v>
+        <v>-0.0373</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3243</v>
+        <v>-1.0385</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7003</v>
+        <v>0.0827</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6193</v>
+        <v>0.7163</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0809</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7593</v>
+        <v>-1.1585</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.354</v>
+        <v>-0.7536</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4052</v>
+        <v>-0.4049</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1488</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.777</v>
+        <v>0.346</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8473000000000001</v>
+        <v>0.4795</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0703</v>
+        <v>-0.1335</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3303</v>
+        <v>-2.5208</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5124</v>
+        <v>-0.8088</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1821</v>
+        <v>-1.7121</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.6627</v>
+        <v>-1.4718</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.7448</v>
+        <v>-0.4597</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9179</v>
+        <v>-1.012</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.1406</v>
+        <v>0.1665</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.3025</v>
+        <v>-0.0359</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1619</v>
+        <v>0.2023</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5221</v>
+        <v>-1.6382</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4423</v>
+        <v>-0.4239</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0797</v>
+        <v>-1.2144</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7348</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>3.2505</v>
+        <v>-0.2174</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2811</v>
+        <v>0.0015</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9694</v>
+        <v>-0.2188</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2772</v>
+        <v>-0.8317</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.8317</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2637</v>
+        <v>-3.1466</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4155</v>
+        <v>-4.0292</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8482</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4718</v>
+        <v>-4.6627</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4597</v>
+        <v>-3.7448</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.012</v>
+        <v>-0.9179</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1665</v>
+        <v>-2.1406</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0359</v>
+        <v>-2.3025</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2023</v>
+        <v>0.1619</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6382</v>
+        <v>-2.5221</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4239</v>
+        <v>-1.4423</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2144</v>
+        <v>-1.0797</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9767</v>
+        <v>2.7348</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9602000000000001</v>
+        <v>1.4342</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6052</v>
+        <v>0.7644</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.355</v>
+        <v>0.6698</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8317</v>
+        <v>0.2772</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0597</v>
+        <v>-3.4374</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7989</v>
+        <v>-3.3944</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2609</v>
+        <v>-0.043</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3493</v>
@@ -2248,13 +2248,13 @@
         <v>1.5627</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7104</v>
+        <v>-0.0881</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6052</v>
+        <v>-0.2008</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1052</v>
+        <v>0.1127</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6093</v>
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8481</v>
+        <v>-4.848099999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>3.628400000000001</v>
+        <v>3.628499999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.476699999999999</v>
+        <v>-8.476599999999998</v>
       </c>
       <c r="G24" t="n">
         <v>-5.6469</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2520000000000009</v>
+        <v>-0.2520000000000007</v>
       </c>
       <c r="I24" t="n">
-        <v>-5.394799999999999</v>
+        <v>-5.3948</v>
       </c>
       <c r="J24" t="n">
         <v>15.1548</v>
@@ -2305,7 +2305,7 @@
         <v>9.078799999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>6.075800000000001</v>
+        <v>6.0758</v>
       </c>
       <c r="M24" t="n">
         <v>-20.8014</v>
@@ -2326,13 +2326,13 @@
         <v>18.5575</v>
       </c>
       <c r="S24" t="n">
-        <v>4.1135</v>
+        <v>4.1134</v>
       </c>
       <c r="T24" t="n">
-        <v>2.3125</v>
+        <v>2.3124</v>
       </c>
       <c r="U24" t="n">
-        <v>1.801</v>
+        <v>1.8011</v>
       </c>
       <c r="V24" t="n">
         <v>-8.1983</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484204_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484204_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.9962</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0493</v>
+        <v>0.8566</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5144</v>
+        <v>1.4452</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4651</v>
+        <v>-0.5886</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8448</v>
+        <v>0.7528</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2336</v>
+        <v>1.1845</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0784</v>
+        <v>-0.4317</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7533</v>
+        <v>2.7499</v>
       </c>
       <c r="K5" t="n">
-        <v>0.944</v>
+        <v>1.9672</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8093</v>
+        <v>0.7827</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9085</v>
+        <v>-1.9971</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1775</v>
+        <v>-0.7828000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.269</v>
+        <v>-1.2144</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>-1.1721</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7202</v>
+        <v>-0.2869</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1134</v>
+        <v>-0.1326</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6068</v>
+        <v>-0.1542</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7061</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8566</v>
+        <v>0.7356</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4452</v>
+        <v>1.0892</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5886</v>
+        <v>-0.3535</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7528</v>
+        <v>0.2226</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1845</v>
+        <v>-1.1798</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4317</v>
+        <v>1.4025</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7499</v>
+        <v>1.391</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9672</v>
+        <v>0.1228</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7827</v>
+        <v>1.2683</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9971</v>
+        <v>-1.1684</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7828000000000001</v>
+        <v>-1.3026</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2144</v>
+        <v>0.1342</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2869</v>
+        <v>-0.5372</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1326</v>
+        <v>-0.3019</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1542</v>
+        <v>-0.2353</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.1219</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7356</v>
+        <v>0.607</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0892</v>
+        <v>0.607</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3535</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2226</v>
+        <v>0.607</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1798</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4025</v>
+        <v>0.607</v>
       </c>
       <c r="J7" t="n">
-        <v>1.391</v>
+        <v>0.607</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1228</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2683</v>
+        <v>0.607</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1684</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3026</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1342</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5372</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3019</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2353</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1105</v>
+        <v>0.4423</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3731</v>
+        <v>0.9074</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4836</v>
+        <v>-0.4651</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.2378</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4431</v>
+        <v>-0.2336</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9718</v>
+        <v>0.4714</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3437</v>
+        <v>1.1463</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2239</v>
+        <v>0.944</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5675</v>
+        <v>0.2023</v>
       </c>
       <c r="M8" t="n">
-        <v>0.185</v>
+        <v>-0.9085</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2192</v>
+        <v>-1.1775</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4043</v>
+        <v>0.269</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9767</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1488</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
         <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5585</v>
+        <v>-0.7202</v>
       </c>
       <c r="T8" t="n">
-        <v>0.432</v>
+        <v>-0.1134</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1265</v>
+        <v>-0.6068</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.7061</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2781</v>
+        <v>0.1105</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6574</v>
+        <v>-1.3731</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6207</v>
+        <v>1.4836</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5724</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8427</v>
+        <v>-0.4431</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2702</v>
+        <v>0.9718</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0807</v>
+        <v>0.3437</v>
       </c>
       <c r="K9" t="n">
-        <v>1.9455</v>
+        <v>-0.2239</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1352</v>
+        <v>0.5675</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5083</v>
+        <v>0.185</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1028</v>
+        <v>-0.2192</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4054</v>
+        <v>0.4043</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7581</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9301</v>
+        <v>-2.1488</v>
       </c>
       <c r="R9" t="n">
         <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5799</v>
+        <v>0.5585</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3624</v>
+        <v>0.432</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2175</v>
+        <v>0.1265</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4875</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.067</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9862</v>
+        <v>-1.2781</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7931</v>
+        <v>-0.6574</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1931</v>
+        <v>-0.6207</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.953</v>
+        <v>0.5724</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6963</v>
+        <v>0.8427</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2566</v>
+        <v>-0.2702</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3742</v>
+        <v>2.0807</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.449</v>
+        <v>1.9455</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.1352</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3271</v>
+        <v>-1.5083</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2474</v>
+        <v>-1.1028</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0797</v>
+        <v>-0.4054</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7814</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1488</v>
+        <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.13</v>
+        <v>-0.5799</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0185</v>
+        <v>-0.3624</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1116</v>
+        <v>-0.2175</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1219</v>
+        <v>0.4875</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1219</v>
+        <v>-0.067</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1317,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1997</v>
+        <v>-2.9862</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3321</v>
+        <v>-1.7931</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8676</v>
+        <v>-1.1931</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8397</v>
+        <v>-1.953</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1622</v>
+        <v>-1.6963</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3225</v>
+        <v>-0.2566</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8318</v>
+        <v>0.3742</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5705</v>
+        <v>-0.449</v>
       </c>
       <c r="L11" t="n">
-        <v>2.4023</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.6714</v>
+        <v>-2.3271</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5917</v>
+        <v>-1.2474</v>
       </c>
       <c r="O11" t="n">
         <v>-1.0797</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3674</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9301</v>
+        <v>-2.1488</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8708</v>
+        <v>-0.13</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2337</v>
+        <v>-0.0185</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6371</v>
+        <v>-0.1116</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1219</v>
@@ -1328,12 +1378,17 @@
       </c>
       <c r="X11" t="n">
         <v>-0.1219</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,151 +1400,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.453299999999999</v>
+        <v>-3.1997</v>
       </c>
       <c r="E12" t="n">
-        <v>9.081899999999997</v>
+        <v>-1.3321</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.6284</v>
+        <v>-1.8676</v>
       </c>
       <c r="G12" t="n">
-        <v>5.646699999999999</v>
+        <v>-0.8397</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2521</v>
+        <v>-2.1622</v>
       </c>
       <c r="I12" t="n">
-        <v>5.394900000000001</v>
+        <v>1.3225</v>
       </c>
       <c r="J12" t="n">
-        <v>20.8015</v>
+        <v>1.8318</v>
       </c>
       <c r="K12" t="n">
-        <v>9.3309</v>
+        <v>-0.5705</v>
       </c>
       <c r="L12" t="n">
-        <v>11.4707</v>
+        <v>2.4023</v>
       </c>
       <c r="M12" t="n">
-        <v>-15.1546</v>
+        <v>-2.6714</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.078899999999999</v>
+        <v>-1.5917</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.075799999999999</v>
+        <v>-1.0797</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.8835</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q12" t="n">
-        <v>-18.5575</v>
+        <v>-2.9301</v>
       </c>
       <c r="R12" t="n">
-        <v>13.674</v>
+        <v>1.5627</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.5082</v>
+        <v>-0.8708</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1958</v>
+        <v>-0.2337</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.3124</v>
+        <v>-0.6371</v>
       </c>
       <c r="V12" t="n">
-        <v>8.1982</v>
+        <v>-0.1219</v>
       </c>
       <c r="W12" t="n">
-        <v>8.033799999999999</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1643999999999999</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CB. CORNELLÀ</t>
+          <t>DM GROUP MOLLET</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6702</v>
+        <v>5.453299999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>6.239</v>
+        <v>9.081900000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5688</v>
+        <v>-3.6284</v>
       </c>
       <c r="G13" t="n">
-        <v>4.3507</v>
+        <v>5.646699999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3661</v>
+        <v>0.2521000000000009</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9846</v>
+        <v>5.3949</v>
       </c>
       <c r="J13" t="n">
-        <v>6.1288</v>
+        <v>20.8015</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1993</v>
+        <v>9.3309</v>
       </c>
       <c r="L13" t="n">
-        <v>1.9295</v>
+        <v>11.4707</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7781</v>
+        <v>-15.1546</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-9.078900000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9449</v>
+        <v>-6.0758</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9534</v>
+        <v>-4.8835</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-18.5575</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9534</v>
+        <v>13.674</v>
       </c>
       <c r="S13" t="n">
-        <v>0.194</v>
+        <v>-3.5082</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1102</v>
+        <v>-1.1958</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0838</v>
+        <v>-2.3124</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.8279</v>
+        <v>8.1982</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>8.033799999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.8279</v>
-      </c>
+        <v>0.1643999999999999</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>G. PEREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2992</v>
+        <v>2.8422</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9456</v>
+        <v>4.4111</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3536</v>
+        <v>-1.5688</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0564</v>
+        <v>2.5227</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8944</v>
+        <v>2.7521</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1621</v>
+        <v>-0.2294</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6947</v>
+        <v>4.3009</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4531</v>
+        <v>3.5853</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2416</v>
+        <v>0.7156</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6382</v>
+        <v>-1.7781</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5587</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0795</v>
+        <v>-0.9449</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1609</v>
+        <v>0.194</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0728</v>
+        <v>0.1102</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2337</v>
+        <v>0.0838</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2772</v>
+        <v>-1.8279</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. VIEJO ANDREU</t>
+          <t>G. PÉREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1645,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.479</v>
+        <v>1.8279</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3</v>
+        <v>1.8279</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.821</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9133</v>
+        <v>1.8279</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0619</v>
+        <v>0.614</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1486</v>
+        <v>1.214</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8226</v>
+        <v>1.8279</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2456</v>
+        <v>0.614</v>
       </c>
       <c r="L15" t="n">
-        <v>2.577</v>
+        <v>1.214</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.7358</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3075</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.4283</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8062</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4541</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3521</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1640,12 +1706,17 @@
       </c>
       <c r="X15" t="n">
         <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. MONSALVE SANZ</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.024</v>
+        <v>1.2992</v>
       </c>
       <c r="E16" t="n">
-        <v>0.102</v>
+        <v>0.9456</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.078</v>
+        <v>0.3536</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2133</v>
+        <v>1.0564</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.8944</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.135</v>
+        <v>0.1621</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0614</v>
+        <v>2.6947</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0614</v>
+        <v>1.4531</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.2416</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2747</v>
+        <v>-1.6382</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1397</v>
+        <v>-0.5587</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.135</v>
+        <v>-1.0795</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0419</v>
+        <v>0.1609</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0406</v>
+        <v>-0.0728</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0014</v>
+        <v>0.2337</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0569</v>
+        <v>1.2279</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2181</v>
+        <v>1.2279</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.275</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2105</v>
+        <v>1.2279</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3512</v>
+        <v>1.2279</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.5618</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1767</v>
+        <v>1.2279</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5239</v>
+        <v>1.2279</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3472</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.3872</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1727</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2146</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.177</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7176</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4593</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6776</v>
+        <v>1.221</v>
       </c>
       <c r="E18" t="n">
-        <v>1.19</v>
+        <v>1.221</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8676</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0983</v>
+        <v>1.221</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5054999999999999</v>
+        <v>0.614</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5928</v>
+        <v>0.607</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0377</v>
+        <v>1.221</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4159</v>
+        <v>0.614</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6218</v>
+        <v>0.607</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.136</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.9215</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2146</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.604</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.461</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.5507</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>F. VIEJO ANDREU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7048</v>
+        <v>0.479</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.696</v>
+        <v>2.3</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-1.821</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9409999999999999</v>
+        <v>-0.9133</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2653</v>
+        <v>-1.0619</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3243</v>
+        <v>0.1486</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7003</v>
+        <v>2.8226</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6193</v>
+        <v>0.2456</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0809</v>
+        <v>2.577</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7593</v>
+        <v>-3.7358</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.354</v>
+        <v>-1.3075</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4052</v>
+        <v>-2.4283</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3453</v>
+        <v>0.8062</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4429</v>
+        <v>0.4541</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.3521</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>P. MONSALVE SANZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7764</v>
+        <v>0.024</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5622</v>
+        <v>0.102</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3385</v>
+        <v>-0.078</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0758</v>
+        <v>-0.2133</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0373</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0385</v>
+        <v>-0.135</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0827</v>
+        <v>0.0614</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7163</v>
+        <v>0.0614</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1585</v>
+        <v>-0.2747</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7536</v>
+        <v>-0.1397</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4049</v>
+        <v>-0.135</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S20" t="n">
-        <v>0.346</v>
+        <v>0.0419</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4795</v>
+        <v>0.0406</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1335</v>
+        <v>0.0014</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5208</v>
+        <v>-0.6776</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8088</v>
+        <v>1.19</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7121</v>
+        <v>-1.8676</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4718</v>
+        <v>-1.0983</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4597</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.012</v>
+        <v>-0.5928</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1665</v>
+        <v>2.0377</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0359</v>
+        <v>1.4159</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2023</v>
+        <v>0.6218</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6382</v>
+        <v>-3.136</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4239</v>
+        <v>-1.9215</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2144</v>
+        <v>-1.2146</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9767</v>
+        <v>2.3441</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2174</v>
+        <v>0.604</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0015</v>
+        <v>0.461</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2188</v>
+        <v>0.143</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8317</v>
+        <v>-1.5507</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8317</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>M. FENES HERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1466</v>
+        <v>-0.7764</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0292</v>
+        <v>0.5622</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8826000000000001</v>
+        <v>-1.3385</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.6627</v>
+        <v>-1.0758</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.7448</v>
+        <v>-0.0373</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9179</v>
+        <v>-1.0385</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.1406</v>
+        <v>0.0827</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.3025</v>
+        <v>0.7163</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1619</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5221</v>
+        <v>-1.1585</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4423</v>
+        <v>-0.7536</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0797</v>
+        <v>-0.4049</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7348</v>
+        <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4342</v>
+        <v>0.346</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7644</v>
+        <v>0.4795</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6698</v>
+        <v>-0.1335</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2772</v>
+        <v>-1.2186</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4374</v>
+        <v>-1.2778</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3944</v>
+        <v>-0.0028</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.043</v>
+        <v>-1.275</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3493</v>
+        <v>-1.4315</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.2415</v>
+        <v>1.7373</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1078</v>
+        <v>-3.1688</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.576</v>
+        <v>0.9557</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.8176</v>
+        <v>2.9099</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2416</v>
+        <v>-1.9542</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7733</v>
+        <v>-2.3872</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4239</v>
+        <v>-1.1727</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3494</v>
+        <v>-1.2146</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0881</v>
+        <v>1.177</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2008</v>
+        <v>0.7176</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1127</v>
+        <v>0.4593</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0549</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. MARTINEZ FERIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,401 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.848099999999999</v>
+        <v>-1.9328</v>
       </c>
       <c r="E24" t="n">
-        <v>3.628499999999999</v>
+        <v>-1.924</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.476599999999998</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.6469</v>
+        <v>-0.287</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2520000000000007</v>
+        <v>0.0373</v>
       </c>
       <c r="I24" t="n">
+        <v>-0.3243</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.4723</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0809</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.7593</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.354</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.4052</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.3453</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.4429</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>U. FERNANDEZ RUIZ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-2.5208</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.8088</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.7121</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.4718</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.4597</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.012</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.1665</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.0359</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.2023</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.6382</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.4239</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-1.2144</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.2174</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.2188</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.8317</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.8317</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>L. MARTOS RUS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-3.1466</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-4.0292</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.8826000000000001</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-4.6627</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-3.7448</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.9179</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-2.1406</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-2.3025</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-2.5221</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.4423</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.0797</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.7348</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.4342</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.7644</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.6698</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A. SAMAKE EL ALAOUI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-3.4374</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-3.3944</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-2.3493</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-2.2415</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.1078</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.576</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-1.8176</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.2416</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1.7733</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.4239</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-1.3494</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.0881</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.2008</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.1127</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484204_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-4.848199999999999</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.628500000000001</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-8.476599999999999</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-5.6471</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.2519999999999989</v>
+      </c>
+      <c r="I28" t="n">
         <v>-5.3948</v>
       </c>
-      <c r="J24" t="n">
-        <v>15.1548</v>
-      </c>
-      <c r="K24" t="n">
-        <v>9.078799999999999</v>
-      </c>
-      <c r="L24" t="n">
-        <v>6.0758</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="J28" t="n">
+        <v>15.1547</v>
+      </c>
+      <c r="K28" t="n">
+        <v>9.078800000000001</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6.0759</v>
+      </c>
+      <c r="M28" t="n">
         <v>-20.8014</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N28" t="n">
         <v>-9.331</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O28" t="n">
         <v>-11.4705</v>
       </c>
-      <c r="P24" t="n">
-        <v>4.883500000000001</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="P28" t="n">
+        <v>4.883499999999999</v>
+      </c>
+      <c r="Q28" t="n">
         <v>-13.6738</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R28" t="n">
         <v>18.5575</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S28" t="n">
         <v>4.1134</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T28" t="n">
         <v>2.3124</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U28" t="n">
         <v>1.8011</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V28" t="n">
         <v>-8.1983</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W28" t="n">
         <v>-0.1647</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X28" t="n">
         <v>-8.0337</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
